--- a/output/pdf_financials_xlsx/CDVA.xlsx
+++ b/output/pdf_financials_xlsx/CDVA.xlsx
@@ -7004,7 +7004,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">

--- a/output/pdf_financials_xlsx/CDVA.xlsx
+++ b/output/pdf_financials_xlsx/CDVA.xlsx
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>2.72668</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -2682,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>1.565614</v>
       </c>
     </row>
     <row r="113">
@@ -5648,7 +5648,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>2.72668</v>
       </c>

--- a/output/pdf_financials_xlsx/CDVA.xlsx
+++ b/output/pdf_financials_xlsx/CDVA.xlsx
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.061319</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.026741</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -5044,7 +5044,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>0.061319</v>
       </c>
@@ -5144,7 +5148,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>-0.01512</v>
       </c>
@@ -6366,7 +6374,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>1.98181</v>
       </c>
